--- a/output/roomself_excel/14690.xlsx
+++ b/output/roomself_excel/14690.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>150722</v>
+        <v>464635</v>
       </c>
       <c r="D2" t="n">
-        <v>3108</v>
+        <v>6092</v>
       </c>
       <c r="E2" t="n">
-        <v>406</v>
+        <v>943</v>
       </c>
       <c r="F2" t="n">
-        <v>314</v>
+        <v>601</v>
       </c>
     </row>
     <row r="3">
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>496843</v>
+        <v>461548</v>
       </c>
       <c r="D3" t="n">
-        <v>6796</v>
+        <v>6060</v>
       </c>
       <c r="E3" t="n">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="F3" t="n">
         <v>601</v>
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>113202</v>
+        <v>150722</v>
       </c>
       <c r="D4" t="n">
-        <v>2692</v>
+        <v>3108</v>
       </c>
       <c r="E4" t="n">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="F4" t="n">
-        <v>364</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>113190</v>
+        <v>113202</v>
       </c>
       <c r="D5" t="n">
         <v>2692</v>
       </c>
       <c r="E5" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F5" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>493939</v>
+        <v>113190</v>
       </c>
       <c r="D6" t="n">
-        <v>6768</v>
+        <v>2692</v>
       </c>
       <c r="E6" t="n">
-        <v>937</v>
+        <v>374</v>
       </c>
       <c r="F6" t="n">
-        <v>601</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>56123</v>
+        <v>122298</v>
       </c>
       <c r="D8" t="n">
-        <v>2492</v>
+        <v>2804</v>
       </c>
       <c r="E8" t="n">
-        <v>187</v>
+        <v>347</v>
       </c>
       <c r="F8" t="n">
-        <v>105</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>36146</v>
+        <v>122417</v>
       </c>
       <c r="D9" t="n">
-        <v>1584</v>
+        <v>2808</v>
       </c>
       <c r="E9" t="n">
-        <v>176</v>
+        <v>388</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17653</v>
+        <v>56123</v>
       </c>
       <c r="D10" t="n">
-        <v>1064</v>
+        <v>2492</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -686,17 +686,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>122298</v>
+        <v>55808</v>
       </c>
       <c r="D12" t="n">
-        <v>2804</v>
+        <v>2484</v>
       </c>
       <c r="E12" t="n">
-        <v>347</v>
+        <v>94</v>
       </c>
       <c r="F12" t="n">
         <v>31</v>
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>83790</v>
+        <v>28544</v>
       </c>
       <c r="D13" t="n">
-        <v>2348</v>
+        <v>1404</v>
       </c>
       <c r="E13" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>35642</v>
+        <v>32208</v>
       </c>
       <c r="D14" t="n">
-        <v>1572</v>
+        <v>1436</v>
       </c>
       <c r="E14" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55808</v>
+        <v>22326</v>
       </c>
       <c r="D15" t="n">
-        <v>2484</v>
+        <v>1220</v>
       </c>
       <c r="E15" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -774,14 +774,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28544</v>
+        <v>32391</v>
       </c>
       <c r="D16" t="n">
-        <v>1404</v>
+        <v>1440</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -796,14 +796,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18560</v>
+        <v>21777</v>
       </c>
       <c r="D17" t="n">
-        <v>1092</v>
+        <v>1208</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -818,14 +818,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22326</v>
+        <v>17653</v>
       </c>
       <c r="D18" t="n">
-        <v>1220</v>
+        <v>1064</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>122417</v>
+        <v>18560</v>
       </c>
       <c r="D19" t="n">
-        <v>2808</v>
+        <v>1092</v>
       </c>
       <c r="E19" t="n">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>66970</v>
+        <v>36146</v>
       </c>
       <c r="D20" t="n">
-        <v>2188</v>
+        <v>1584</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>83349</v>
+        <v>83790</v>
       </c>
       <c r="D21" t="n">
-        <v>2344</v>
+        <v>2348</v>
       </c>
       <c r="E21" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F21" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21777</v>
+        <v>35642</v>
       </c>
       <c r="D22" t="n">
-        <v>1208</v>
+        <v>1572</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -932,15 +932,59 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>66970</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2188</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>83349</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2344</v>
+      </c>
+      <c r="E24" t="n">
+        <v>374</v>
+      </c>
+      <c r="F24" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>66063</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D25" t="n">
         <v>1454</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/roomself_excel/14690.xlsx
+++ b/output/roomself_excel/14690.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>6092</v>
       </c>
-      <c r="E2" t="n">
-        <v>943</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>601</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>277</v>
+      </c>
+      <c r="J2" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +533,20 @@
       <c r="D3" t="n">
         <v>6060</v>
       </c>
-      <c r="E3" t="n">
-        <v>937</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>601</v>
-      </c>
+        <v>875</v>
+      </c>
+      <c r="G3" t="n">
+        <v>32</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>3108</v>
       </c>
-      <c r="E4" t="n">
-        <v>406</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>314</v>
+        <v>374</v>
+      </c>
+      <c r="G4" t="n">
+        <v>33</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>281</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +601,27 @@
       <c r="D5" t="n">
         <v>2692</v>
       </c>
-      <c r="E5" t="n">
-        <v>373</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>364</v>
+        <v>342</v>
+      </c>
+      <c r="G5" t="n">
+        <v>33</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>331</v>
+      </c>
+      <c r="J5" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -563,11 +639,27 @@
       <c r="D6" t="n">
         <v>2692</v>
       </c>
-      <c r="E6" t="n">
-        <v>374</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>362</v>
+        <v>343</v>
+      </c>
+      <c r="G6" t="n">
+        <v>32</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>330</v>
+      </c>
+      <c r="J6" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +677,20 @@
       <c r="D7" t="n">
         <v>3116</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>379</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>32</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +707,20 @@
       <c r="D8" t="n">
         <v>2804</v>
       </c>
-      <c r="E8" t="n">
-        <v>347</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
+        <v>336</v>
+      </c>
+      <c r="G8" t="n">
         <v>31</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +737,27 @@
       <c r="D9" t="n">
         <v>2808</v>
       </c>
-      <c r="E9" t="n">
-        <v>388</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>308</v>
+        <v>276</v>
+      </c>
+      <c r="G9" t="n">
+        <v>32</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>345</v>
+      </c>
+      <c r="J9" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +775,20 @@
       <c r="D10" t="n">
         <v>2492</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>94</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>31</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +805,12 @@
       <c r="D11" t="n">
         <v>1404</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +827,20 @@
       <c r="D12" t="n">
         <v>2484</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>94</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>31</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +857,12 @@
       <c r="D13" t="n">
         <v>1404</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +879,12 @@
       <c r="D14" t="n">
         <v>1436</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +901,12 @@
       <c r="D15" t="n">
         <v>1220</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +923,12 @@
       <c r="D16" t="n">
         <v>1440</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +945,12 @@
       <c r="D17" t="n">
         <v>1208</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +967,12 @@
       <c r="D18" t="n">
         <v>1064</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +989,12 @@
       <c r="D19" t="n">
         <v>1092</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1011,20 @@
       <c r="D20" t="n">
         <v>1584</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>176</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>31</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,11 +1041,27 @@
       <c r="D21" t="n">
         <v>2348</v>
       </c>
-      <c r="E21" t="n">
-        <v>373</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>276</v>
+        <v>245</v>
+      </c>
+      <c r="G21" t="n">
+        <v>31</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>342</v>
+      </c>
+      <c r="J21" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="22">
@@ -915,12 +1079,20 @@
       <c r="D22" t="n">
         <v>1572</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>173</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>31</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1109,12 @@
       <c r="D23" t="n">
         <v>2188</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,11 +1131,27 @@
       <c r="D24" t="n">
         <v>2344</v>
       </c>
-      <c r="E24" t="n">
-        <v>374</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>275</v>
+        <v>243</v>
+      </c>
+      <c r="G24" t="n">
+        <v>31</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>343</v>
+      </c>
+      <c r="J24" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="25">
@@ -981,12 +1169,12 @@
       <c r="D25" t="n">
         <v>1454</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/14690.xlsx
+++ b/output/roomself_excel/14690.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,66 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -517,6 +577,54 @@
       <c r="J2" t="n">
         <v>31</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>269</v>
+      </c>
+      <c r="N2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>86</v>
+      </c>
+      <c r="R2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>123</v>
+      </c>
+      <c r="V2" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -547,6 +655,42 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>386</v>
+      </c>
+      <c r="N3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>83</v>
+      </c>
+      <c r="R3" t="n">
+        <v>32</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -585,6 +729,30 @@
       <c r="J4" t="n">
         <v>32</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>189</v>
+      </c>
+      <c r="N4" t="n">
+        <v>33</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -623,6 +791,30 @@
       <c r="J5" t="n">
         <v>31</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>124</v>
+      </c>
+      <c r="N5" t="n">
+        <v>33</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -661,6 +853,30 @@
       <c r="J6" t="n">
         <v>31</v>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>127</v>
+      </c>
+      <c r="N6" t="n">
+        <v>32</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -691,6 +907,30 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>192</v>
+      </c>
+      <c r="N7" t="n">
+        <v>32</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -721,6 +961,30 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>123</v>
+      </c>
+      <c r="N8" t="n">
+        <v>31</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -759,6 +1023,30 @@
       <c r="J9" t="n">
         <v>32</v>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>124</v>
+      </c>
+      <c r="N9" t="n">
+        <v>32</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -789,6 +1077,30 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>63</v>
+      </c>
+      <c r="N10" t="n">
+        <v>31</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -811,6 +1123,18 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -841,6 +1165,30 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>62</v>
+      </c>
+      <c r="N12" t="n">
+        <v>31</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -863,6 +1211,18 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -885,6 +1245,18 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -907,6 +1279,18 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -929,6 +1313,18 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -951,6 +1347,18 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -973,6 +1381,18 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -995,6 +1415,18 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1025,6 +1457,30 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>65</v>
+      </c>
+      <c r="N20" t="n">
+        <v>31</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1063,6 +1519,42 @@
       <c r="J21" t="n">
         <v>31</v>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>92</v>
+      </c>
+      <c r="N21" t="n">
+        <v>31</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>84</v>
+      </c>
+      <c r="R21" t="n">
+        <v>31</v>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1093,6 +1585,30 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>63</v>
+      </c>
+      <c r="N22" t="n">
+        <v>31</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1115,6 +1631,18 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1153,6 +1681,42 @@
       <c r="J24" t="n">
         <v>32</v>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>97</v>
+      </c>
+      <c r="N24" t="n">
+        <v>31</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>84</v>
+      </c>
+      <c r="R24" t="n">
+        <v>32</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1175,6 +1739,18 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
